--- a/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/preflight/validacao-integridade.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/preflight/validacao-integridade.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Violações'!$A$1:$H$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Violações'!$A$1:$H$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resumo'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR105', 'MR108']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpenAI: HTTP Error 502: Bad Gateway; body: {"error":{"message":"fetch failed","type":"upstream_error","code":"upstream_failure"}}</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: escopo_motivos: motivos esperados=['MR019', 'MR021']; recebidos=[]</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR026', 'MR028']; recebidos=[]</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>codigo_item_duplicado: itens duplicados: A6G23; escopo_itens: itens esperados=['A6G23']; recebidos=['A6G23', 'A6G23', 'A6G23', 'A6G23']; escopo_motivos: motivos esperados=['MR103', 'MR105', 'MR107']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido; escopo_motivos: motivos esperados=['MR103', 'MR105', 'MR107']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido; escopo_motivos: motivos esperados=['MR103', 'MR105', 'MR107']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido; escopo_motivos: motivos esperados=['MR103', 'MR105', 'MR107']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: escopo_motivos: motivos esperados=['MR002', 'MR005']; recebidos=[]</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR008', 'MR010', 'MR012', 'MR014']; recebidos=['MR008', 'MR010', ':', 'MR014']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR022', 'MR024', 'MR026', 'MR028']; recebidos=['MR022', 'MR024', ':', 'MR028']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR057', 'MR058', 'MR059', 'MR060']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR103', 'MR105', 'MR107', 'MR109']; recebidos=['MR103', 'MR105', 'MR107', ':']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR019', 'MR020']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR026']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; escopo_motivos: motivos esperados=['MR037', 'MR039']; recebidos=[]</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR034', 'MR036', 'MR038']; recebidos=['MR034', 'MR036', ':']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR085', 'MR087', 'MR089']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR036', 'MR038']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR054', 'MR056']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR022', 'MR024', 'MR026', 'MR028']; recebidos=['MR022', 'MR024', ':', 'MR028']; estado_motivo: estados de motivo inválidos: inconclusivo; coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: GEMINI_API_KEY nao configurada para provider gemini</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR044']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpencodeGo: HTTP Error 503: Service Unavailable</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpencodeGo: The read operation timed out</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 1] Operation not permitted&gt;</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR049']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3870,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR051', 'MR053', 'MR055']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: escopo_motivos: motivos esperados=['MR018', 'MR021']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -3996,12 +3996,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR031']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR087']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4206,12 +4206,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>estado_motivo: estados de motivo inválidos: inconclusivo; coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR075', 'MR077', 'MR079']; recebidos=['MR075', 'MR077', ':']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR045']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4542,12 +4542,12 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR091', 'MR093', 'MR095', 'MR097', 'MR099']; recebidos=['MR091', 'MR093', ':', 'MR097', 'MR099']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR075', 'MR077', 'MR079']; recebidos=['MR075', 'MR077', ':']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4794,12 +4794,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -4920,12 +4920,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -4962,12 +4962,12 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR081', 'MR083']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5046,12 +5046,12 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>codigo_item_duplicado: itens duplicados: A6G23; escopo_itens: itens esperados=['A6G23']; recebidos=['A6G23', 'A6G23']; escopo_motivos: motivos esperados=['MR106', 'MR108']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido; escopo_motivos: motivos esperados=['MR106', 'MR108']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5214,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5340,12 +5340,12 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR102']; recebidos=[]; coerencia_temporal: situação mantida exige ao menos um motivo mantido</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpencodeGo: The read operation timed out</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>escopo_motivos: motivos esperados=['MR081', 'MR083']; recebidos=[]</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -5886,12 +5886,12 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>coerencia_temporal: corrigida_posteriormente exige todos os motivos afastados</t>
+          <t>status error: GEMINI_API_KEY nao configurada para provider gemini</t>
         </is>
       </c>
     </row>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>estado_temporal: estado temporal inválido na conclusão 0: 'inconclusiva'; estado_motivo: estados de motivo inválidos: inconclusivo</t>
+          <t>status error: erro ao chamar OpenAI: &lt;urlopen error [Errno 111] Connection refused&gt;</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpencodeGo: HTTP Error 400: Bad Request; body: {"error":{"message":"Error from provider (Alibaba): &lt;400&gt; InternalError.Algo.InvalidParameter: Model output became abnormal while generating a JSON response for response_format. The generation was aborted because the partial output may be incomplete or invalid JSON. Please retry the request or adjust your prompt or JSON schema.","type":"invalid_request_error","param":null,"code":"invalid_parameter_error"},"id":"chatcmpl-df0143bd-3aa4-4485-a55c-fb8145550870","request_id":"df0143bd-3aa4-4485-a55c-fb8145550870"}</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6128,22 +6128,22 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>de33aea4c0daa4d9c203fd66ca0d66204dd8eef63cd4f92389753a27c13f5e33</t>
+          <t>4bfb9d778ba73519318db54ed1166c99006688fca24cf17d3b474f1ae3d36ed9</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>minimax-m3</t>
+          <t>qwen3.7-plus</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>escopo_itens: itens esperados=['q2504', 'q2504ext[A]', 'q2504ext[B]', 'q2504ext[C]', 'q2504ext[D]', 'q2504ext[E]', 'q2504ext[F]', 'q2504ext[G]', 'q2504ext[H]', 'q2504ext[I]', 'q2504ext[J]']; recebidos=['q2504']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6180,12 +6180,12 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpencodeGo: The read operation timed out</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>19fe180c06035e633a037ddc4afd1e415e1cb7d4f6cdc04d69f3a53082ce9ae5</t>
+          <t>abf0c14116149ec884c3deb7e339f617e594bca8f72469070d714ae8628bd056</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>status error: erro ao chamar OpencodeGo: HTTP Error 503: Service Unavailable</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: escopo_itens: itens esperados=['q2203', 'q2203ext[A]', 'q2203ext[B]']; recebidos=['q2203', 'q2203ext[A]', 'q2203ext[B]', 'q2203ext[C]']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6328,17 +6328,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>NOVA IGUAÇU</t>
+          <t>RIOPREVIDENCIA</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>q1001</t>
+          <t>q2102</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>353b74b94e7fb27657b495b9c59d5aece54214d8d15d334107aa528361a55d7e</t>
+          <t>ea56c39f3e27bd1a43f1a2be5d911473c48b9cb77b03fbff56dbb7811d04bb56</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>q2102</t>
+          <t>q2504</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>ea56c39f3e27bd1a43f1a2be5d911473c48b9cb77b03fbff56dbb7811d04bb56</t>
+          <t>dfe9a3b4a4f84aaab8bcf4bbae79bd60a7ed966f3dacd50ae60f62bfdba61336</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6412,17 +6412,17 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>RIOPREVIDENCIA</t>
+          <t>SÃO PEDRO DA ALDEIA</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>q2203</t>
+          <t>q2101</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>720d7d0873d454336c136deab5fc45929ce79b4ac2965b47beefa088ab70d745</t>
+          <t>f813304532ef66f67ac1cd1452d7b9cc880b47461b33bd31a3e37e21ef61bfdd</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6454,17 +6454,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>RIOPREVIDENCIA</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>q2504</t>
+          <t>q1002</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>dfe9a3b4a4f84aaab8bcf4bbae79bd60a7ed966f3dacd50ae60f62bfdba61336</t>
+          <t>1890bd0a40c46434e7f71228ffe5659dd503ac6f4e9346bec1be0977e5ecb5ed</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6496,17 +6496,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>SÃO PEDRO DA ALDEIA</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>q2101</t>
+          <t>q2504</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>f813304532ef66f67ac1cd1452d7b9cc880b47461b33bd31a3e37e21ef61bfdd</t>
+          <t>d68924abbfd9689256deb771f1fb55726799231fc7a67f27fb37a5c5e2a012f6</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>conclusoes_ausentes: resultado não contém conclusões</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>fbd0f7da4b316564db3995960c305bfac3e20e211a8378f8d4b5a3bfb26b80de</t>
+          <t>c08b84d8a560d74376e572af5ae5d07fd35765d96755a5a4f2ced3058d8245f7</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>status error: resposta fora do escopo lógico do caso: escopo_itens: itens esperados=['q2204', 'q2204ext[A]', 'q2204ext[B]', 'q2204ext[D]', 'q2204ext[E]', 'q2204ext[F]']; recebidos=['q2204', 'q2204ext[A]', 'q2204ext[B]', 'q2204ext[C]', 'q2204ext[D]', 'q2204ext[E]', 'q2204ext[F]']</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
@@ -6600,747 +6600,17 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>codigo_item_duplicado: itens duplicados: q2804[A]; escopo_itens: itens esperados=['q2804[A]']; recebidos=['q2804[A]', 'q2804[A]']</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>avaliação individual</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>TJRJ</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>q2708</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>106bcb1bd945edcc8b8fb6be9cbd11e76f87114eaf74c13d6a3f06077d4e7f90</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>qwen3.7-plus</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>status error: erro ao chamar OpencodeGo: The read operation timed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>ARRAIAL DO CABO</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>q1001</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>4232840715c928cf6ee8fe7075f49f09c0d1b1fc4f1c15e8d36d8c2d27945ca8</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>CAMPOS DOS GOYTACAZES</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>q2702</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>235302a19d9856d0c0782d0ac2811f14e5ac9b2db301bee8cf7680f244c7f689</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>CECIERJ</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>q1001</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>ee18bea5be42ff5d2a6b761fba1fa1fef99a3962985baa19837c63a9d49dcbbe</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>CGE</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>q2203</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>9ee180d4d07734566091c478b539f4038c08c33719aa841cc2c9f25cc47fbfd0</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>gemini-3.5-flash-lite</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>status error: parecer inválido após correção: texto publicável: conclusão referencia documentos sem anexo ou link comprobatório; caso sem anexo ou link deve informar que a organização não apresentou documentação comprobatória; caso sem anexo ou link não pode declarar evidência apresentada</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>IPEM</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>q2101</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>630dc1b95e8727983ff2d3f56be56e3b8206743cbd646de29e0e9d1b6d19179b</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>IPEM</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>q2102</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>5610c374c926afbb84b45d7828c6bc807190b1f45835a3651f2ff210d572278c</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>IPEM</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>q2203</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>ab1120581710837f60cc93a585e5d2db3966860ad8c179f6a455fd91767a0834</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>IPEM</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>q2504</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>de33aea4c0daa4d9c203fd66ca0d66204dd8eef63cd4f92389753a27c13f5e33</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>MPERJ</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>q2102</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>f829bd82e203e63dd268d5a4127d6a3ccc035f6bf999298f35cd8a54b9b2def5</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>MPERJ</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>q2201</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>19fe180c06035e633a037ddc4afd1e415e1cb7d4f6cdc04d69f3a53082ce9ae5</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>NOVA IGUAÇU</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>q1001</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>353b74b94e7fb27657b495b9c59d5aece54214d8d15d334107aa528361a55d7e</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>RIO DAS OSTRAS</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>q1001</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>c0c9b35b1edc837e2a71d9452872c184ca3fd27f6fc10a7fd677be29f1eceed8</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>RIOPREVIDENCIA</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>q2203</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>720d7d0873d454336c136deab5fc45929ce79b4ac2965b47beefa088ab70d745</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>SEINFRA</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>q1002</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>eaa693ab0a1f38c788295019fca2779dc37c2d68d680928ba6cd488d5263c770</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>SEINFRA</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>q2504</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>95f7d097bfa1e260fc8eaf7d7bfc6b8496d8f5def0e230c32e7925fea6891360</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>SETD</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>q2204</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>fbd0f7da4b316564db3995960c305bfac3e20e211a8378f8d4b5a3bfb26b80de</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>TJRJ</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>q2708</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>106bcb1bd945edcc8b8fb6be9cbd11e76f87114eaf74c13d6a3f06077d4e7f90</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>TJRJ</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>q2804</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>927e0aa31ea3fb45bfd42331e950faf05b9ed68d759b57a29776dac055ce01da</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>ausente</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>parecer consolidado ausente</t>
+          <t>status error: OPENCODEGO_API_KEY nao configurada para provider opencodego</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H166"/>
+  <autoFilter ref="A1:H147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7384,7 +6654,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>reparo_necessario</t>
+          <t>conforme</t>
         </is>
       </c>
     </row>
@@ -7395,7 +6665,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5">
@@ -7405,7 +6675,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>583</v>
+        <v>598</v>
       </c>
     </row>
     <row r="6">
@@ -7425,7 +6695,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7435,7 +6705,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
